--- a/tests/specs/fixtures/specs_groups.xlsx
+++ b/tests/specs/fixtures/specs_groups.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\MyPy\Packages\fltk\tests\dicz\fixtures\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\MyPy\Packages\fltk\tests\specs\fixtures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C892CB9D-C86C-4324-843B-7183BA630622}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C94072FE-674B-4C24-B275-E54CD6E07857}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="78">
   <si>
     <t>label</t>
   </si>
@@ -254,6 +254,9 @@
   </si>
   <si>
     <t>rule1</t>
+  </si>
+  <si>
+    <t>size=3~shape=dot</t>
   </si>
 </sst>
 </file>
@@ -759,7 +762,7 @@
         <v>31</v>
       </c>
       <c r="H4" t="s">
-        <v>5</v>
+        <v>77</v>
       </c>
       <c r="I4" t="s">
         <v>5</v>

--- a/tests/specs/fixtures/specs_groups.xlsx
+++ b/tests/specs/fixtures/specs_groups.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\MyPy\Packages\fltk\tests\specs\fixtures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C94072FE-674B-4C24-B275-E54CD6E07857}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8949221A-B4F6-4A04-A031-45415E3DB9F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="81">
   <si>
     <t>label</t>
   </si>
@@ -133,9 +133,6 @@
     <t>LineGeom</t>
   </si>
   <si>
-    <t>TsFmt</t>
-  </si>
-  <si>
     <t>GtFmt</t>
   </si>
   <si>
@@ -214,12 +211,6 @@
     <t>scale=100~mask={:,.1f}%</t>
   </si>
   <si>
-    <t>scale=100~mask={:,.0f}%</t>
-  </si>
-  <si>
-    <t>scale=0.000001~mask={:,.1f} M$</t>
-  </si>
-  <si>
     <t>CieA</t>
   </si>
   <si>
@@ -257,6 +248,24 @@
   </si>
   <si>
     <t>size=3~shape=dot</t>
+  </si>
+  <si>
+    <t>periods</t>
+  </si>
+  <si>
+    <t>q2021-4, q2022-4, q2023-4, q2024-4, q2025-4</t>
+  </si>
+  <si>
+    <t>q2021-4, q2022-4, q2023-4</t>
+  </si>
+  <si>
+    <t>q2021-4</t>
+  </si>
+  <si>
+    <t>q2021-4, q2022-4, q2023-4, q2024-4</t>
+  </si>
+  <si>
+    <t>q2021-4, q2022-4</t>
   </si>
 </sst>
 </file>
@@ -637,7 +646,8 @@
     <col min="6" max="6" width="38.5703125" customWidth="1"/>
     <col min="7" max="7" width="15.7109375" customWidth="1"/>
     <col min="8" max="8" width="18.7109375" customWidth="1"/>
-    <col min="9" max="10" width="40.7109375" customWidth="1"/>
+    <col min="9" max="9" width="40.7109375" customWidth="1"/>
+    <col min="10" max="10" width="39.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -645,7 +655,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -666,10 +676,10 @@
         <v>35</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>36</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -677,7 +687,7 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C2" t="b">
         <f>FALSE()</f>
@@ -687,7 +697,7 @@
         <v>5</v>
       </c>
       <c r="E2" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F2" t="s">
         <v>23</v>
@@ -696,13 +706,13 @@
         <v>24</v>
       </c>
       <c r="H2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I2" t="s">
         <v>5</v>
       </c>
       <c r="J2" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -710,17 +720,17 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C3" t="b">
         <f>FALSE()</f>
         <v>0</v>
       </c>
       <c r="D3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F3" t="s">
         <v>25</v>
@@ -735,7 +745,7 @@
         <v>5</v>
       </c>
       <c r="J3" t="s">
-        <v>5</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -743,17 +753,17 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C4" t="b">
         <f>FALSE()</f>
         <v>0</v>
       </c>
       <c r="D4" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F4" t="s">
         <v>26</v>
@@ -762,13 +772,13 @@
         <v>31</v>
       </c>
       <c r="H4" t="s">
+        <v>74</v>
+      </c>
+      <c r="I4" t="s">
+        <v>5</v>
+      </c>
+      <c r="J4" t="s">
         <v>77</v>
-      </c>
-      <c r="I4" t="s">
-        <v>5</v>
-      </c>
-      <c r="J4" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -776,14 +786,14 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C5" t="b">
         <f>TRUE()</f>
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F5" t="s">
         <v>27</v>
@@ -797,9 +807,6 @@
       <c r="I5" t="s">
         <v>5</v>
       </c>
-      <c r="J5" t="s">
-        <v>5</v>
-      </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
@@ -813,10 +820,10 @@
         <v>0</v>
       </c>
       <c r="E6" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G6" t="s">
         <v>31</v>
@@ -825,10 +832,7 @@
         <v>5</v>
       </c>
       <c r="I6" t="s">
-        <v>60</v>
-      </c>
-      <c r="J6" t="s">
-        <v>5</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -843,22 +847,19 @@
         <v>0</v>
       </c>
       <c r="E7" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H7" t="s">
         <v>5</v>
       </c>
       <c r="I7" t="s">
-        <v>60</v>
-      </c>
-      <c r="J7" t="s">
-        <v>5</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -873,22 +874,19 @@
         <v>0</v>
       </c>
       <c r="E8" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H8" t="s">
         <v>5</v>
       </c>
       <c r="I8" t="s">
-        <v>60</v>
-      </c>
-      <c r="J8" t="s">
-        <v>5</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -896,7 +894,7 @@
         <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C9" s="2" t="b">
         <f>FALSE()</f>
@@ -918,8 +916,8 @@
       <c r="I9" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="J9" s="2" t="s">
-        <v>5</v>
+      <c r="J9" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -927,7 +925,7 @@
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C10" s="2" t="b">
         <f>FALSE()</f>
@@ -949,8 +947,8 @@
       <c r="I10" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="J10" s="2" t="s">
-        <v>5</v>
+      <c r="J10" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
@@ -965,10 +963,10 @@
         <v>0</v>
       </c>
       <c r="E11" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="F11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G11" t="s">
         <v>31</v>
@@ -977,10 +975,7 @@
         <v>5</v>
       </c>
       <c r="I11" t="s">
-        <v>62</v>
-      </c>
-      <c r="J11" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
@@ -995,22 +990,19 @@
         <v>0</v>
       </c>
       <c r="E12" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="F12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H12" t="s">
         <v>5</v>
       </c>
       <c r="I12" t="s">
-        <v>62</v>
-      </c>
-      <c r="J12" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
@@ -1025,19 +1017,16 @@
         <v>0</v>
       </c>
       <c r="E13" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="F13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H13" t="s">
         <v>5</v>
       </c>
       <c r="I13" t="s">
-        <v>60</v>
-      </c>
-      <c r="J13" t="s">
-        <v>5</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
@@ -1052,16 +1041,13 @@
         <v>1</v>
       </c>
       <c r="F14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H14" t="s">
         <v>5</v>
       </c>
       <c r="I14" t="s">
-        <v>60</v>
-      </c>
-      <c r="J14" t="s">
-        <v>5</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -1076,16 +1062,13 @@
         <v>0</v>
       </c>
       <c r="F15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H15" t="s">
         <v>5</v>
       </c>
       <c r="I15" t="s">
-        <v>62</v>
-      </c>
-      <c r="J15" t="s">
-        <v>5</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
@@ -1100,22 +1083,19 @@
         <v>0</v>
       </c>
       <c r="F16" t="s">
+        <v>49</v>
+      </c>
+      <c r="G16" t="s">
         <v>50</v>
       </c>
-      <c r="G16" t="s">
-        <v>51</v>
-      </c>
       <c r="H16" t="s">
         <v>5</v>
       </c>
       <c r="I16" t="s">
-        <v>61</v>
-      </c>
-      <c r="J16" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>7</v>
       </c>
@@ -1127,22 +1107,19 @@
         <v>0</v>
       </c>
       <c r="F17" t="s">
+        <v>52</v>
+      </c>
+      <c r="G17" t="s">
         <v>53</v>
       </c>
-      <c r="G17" t="s">
-        <v>54</v>
-      </c>
       <c r="H17" t="s">
         <v>5</v>
       </c>
       <c r="I17" t="s">
-        <v>61</v>
-      </c>
-      <c r="J17" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>7</v>
       </c>
@@ -1154,19 +1131,16 @@
         <v>0</v>
       </c>
       <c r="F18" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H18" t="s">
         <v>5</v>
       </c>
       <c r="I18" t="s">
-        <v>61</v>
-      </c>
-      <c r="J18" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>7</v>
       </c>
@@ -1178,22 +1152,19 @@
         <v>0</v>
       </c>
       <c r="F19" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H19" t="s">
         <v>5</v>
       </c>
       <c r="I19" t="s">
-        <v>60</v>
-      </c>
-      <c r="J19" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>7</v>
       </c>
@@ -1205,22 +1176,19 @@
         <v>0</v>
       </c>
       <c r="F20" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G20" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H20" t="s">
         <v>5</v>
       </c>
       <c r="I20" t="s">
-        <v>60</v>
-      </c>
-      <c r="J20" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>7</v>
       </c>
@@ -1232,19 +1200,16 @@
         <v>0</v>
       </c>
       <c r="F21" t="s">
+        <v>56</v>
+      </c>
+      <c r="G21" t="s">
         <v>57</v>
       </c>
-      <c r="G21" t="s">
-        <v>58</v>
-      </c>
       <c r="H21" t="s">
         <v>5</v>
       </c>
       <c r="I21" t="s">
-        <v>62</v>
-      </c>
-      <c r="J21" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>

--- a/tests/specs/fixtures/specs_groups.xlsx
+++ b/tests/specs/fixtures/specs_groups.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\MyPy\Packages\fltk\tests\specs\fixtures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8949221A-B4F6-4A04-A031-45415E3DB9F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B5296AB-2B88-4024-8546-BB9D828C181D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3810" yWindow="3810" windowWidth="28800" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -130,12 +130,6 @@
     <t>black</t>
   </si>
   <si>
-    <t>LineGeom</t>
-  </si>
-  <si>
-    <t>GtFmt</t>
-  </si>
-  <si>
     <t>forestgreen</t>
   </si>
   <si>
@@ -199,18 +193,6 @@
     <t>darkorchid</t>
   </si>
   <si>
-    <t>size=2~shape=dash</t>
-  </si>
-  <si>
-    <t>scale=0.000001~mask={:,.1f}</t>
-  </si>
-  <si>
-    <t>scale=1~mask={:,.2f}</t>
-  </si>
-  <si>
-    <t>scale=100~mask={:,.1f}%</t>
-  </si>
-  <si>
     <t>CieA</t>
   </si>
   <si>
@@ -247,25 +229,43 @@
     <t>rule1</t>
   </si>
   <si>
-    <t>size=3~shape=dot</t>
-  </si>
-  <si>
     <t>periods</t>
   </si>
   <si>
-    <t>q2021-4, q2022-4, q2023-4, q2024-4, q2025-4</t>
-  </si>
-  <si>
-    <t>q2021-4, q2022-4, q2023-4</t>
-  </si>
-  <si>
-    <t>q2021-4</t>
-  </si>
-  <si>
-    <t>q2021-4, q2022-4, q2023-4, q2024-4</t>
-  </si>
-  <si>
-    <t>q2021-4, q2022-4</t>
+    <t>geomLine</t>
+  </si>
+  <si>
+    <t>fmtGt</t>
+  </si>
+  <si>
+    <t>{'scale': 0.000001, 'mask': '{:,.1f}'}</t>
+  </si>
+  <si>
+    <t>{'scale': 100, 'mask': '{:,.1f}%'}</t>
+  </si>
+  <si>
+    <t>{'scale':1, 'mask':'{:,.2f}'}</t>
+  </si>
+  <si>
+    <t>(q2021-4, q2022-4, q2023-4, q2024-4)</t>
+  </si>
+  <si>
+    <t>(q2021-4, q2022-4, q2023-4)</t>
+  </si>
+  <si>
+    <t>(q2021-4, q2022-4)</t>
+  </si>
+  <si>
+    <t>(q2021-4)</t>
+  </si>
+  <si>
+    <t>{'size':2,'shape':'dash'}</t>
+  </si>
+  <si>
+    <t>{'size':3,'shape':'dot'}</t>
+  </si>
+  <si>
+    <t>('q2021-4', 'q2022-4', 'q2023-4', 'q2024-4', 'q2025-4')</t>
   </si>
 </sst>
 </file>
@@ -645,7 +645,7 @@
     <col min="5" max="5" width="16.5703125" customWidth="1"/>
     <col min="6" max="6" width="38.5703125" customWidth="1"/>
     <col min="7" max="7" width="15.7109375" customWidth="1"/>
-    <col min="8" max="8" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="25.7109375" customWidth="1"/>
     <col min="9" max="9" width="40.7109375" customWidth="1"/>
     <col min="10" max="10" width="39.85546875" customWidth="1"/>
   </cols>
@@ -655,7 +655,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -673,13 +673,13 @@
         <v>22</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>35</v>
+        <v>69</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -687,7 +687,7 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C2" t="b">
         <f>FALSE()</f>
@@ -697,7 +697,7 @@
         <v>5</v>
       </c>
       <c r="E2" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="F2" t="s">
         <v>23</v>
@@ -706,13 +706,13 @@
         <v>24</v>
       </c>
       <c r="H2" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="I2" t="s">
         <v>5</v>
       </c>
       <c r="J2" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -720,17 +720,17 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="C3" t="b">
         <f>FALSE()</f>
         <v>0</v>
       </c>
       <c r="D3" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="E3" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="F3" t="s">
         <v>25</v>
@@ -745,7 +745,7 @@
         <v>5</v>
       </c>
       <c r="J3" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -753,17 +753,17 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C4" t="b">
         <f>FALSE()</f>
         <v>0</v>
       </c>
       <c r="D4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="E4" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="F4" t="s">
         <v>26</v>
@@ -772,13 +772,13 @@
         <v>31</v>
       </c>
       <c r="H4" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="I4" t="s">
         <v>5</v>
       </c>
       <c r="J4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -786,14 +786,14 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="C5" t="b">
         <f>TRUE()</f>
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="F5" t="s">
         <v>27</v>
@@ -820,10 +820,10 @@
         <v>0</v>
       </c>
       <c r="E6" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="F6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G6" t="s">
         <v>31</v>
@@ -832,7 +832,7 @@
         <v>5</v>
       </c>
       <c r="I6" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -847,19 +847,19 @@
         <v>0</v>
       </c>
       <c r="E7" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="F7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H7" t="s">
         <v>5</v>
       </c>
       <c r="I7" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -874,19 +874,19 @@
         <v>0</v>
       </c>
       <c r="E8" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="F8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G8" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H8" t="s">
         <v>5</v>
       </c>
       <c r="I8" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -894,7 +894,7 @@
         <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="C9" s="2" t="b">
         <f>FALSE()</f>
@@ -917,7 +917,7 @@
         <v>5</v>
       </c>
       <c r="J9" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -925,7 +925,7 @@
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="C10" s="2" t="b">
         <f>FALSE()</f>
@@ -948,7 +948,7 @@
         <v>5</v>
       </c>
       <c r="J10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
@@ -963,10 +963,10 @@
         <v>0</v>
       </c>
       <c r="E11" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="F11" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G11" t="s">
         <v>31</v>
@@ -975,7 +975,7 @@
         <v>5</v>
       </c>
       <c r="I11" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
@@ -990,19 +990,19 @@
         <v>0</v>
       </c>
       <c r="E12" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="F12" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G12" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H12" t="s">
         <v>5</v>
       </c>
       <c r="I12" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
@@ -1017,16 +1017,16 @@
         <v>0</v>
       </c>
       <c r="E13" t="s">
+        <v>65</v>
+      </c>
+      <c r="F13" t="s">
+        <v>42</v>
+      </c>
+      <c r="H13" t="s">
+        <v>5</v>
+      </c>
+      <c r="I13" t="s">
         <v>71</v>
-      </c>
-      <c r="F13" t="s">
-        <v>44</v>
-      </c>
-      <c r="H13" t="s">
-        <v>5</v>
-      </c>
-      <c r="I13" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
@@ -1041,13 +1041,13 @@
         <v>1</v>
       </c>
       <c r="F14" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H14" t="s">
         <v>5</v>
       </c>
       <c r="I14" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -1062,13 +1062,13 @@
         <v>0</v>
       </c>
       <c r="F15" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H15" t="s">
         <v>5</v>
       </c>
       <c r="I15" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
@@ -1083,16 +1083,16 @@
         <v>0</v>
       </c>
       <c r="F16" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G16" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="H16" t="s">
         <v>5</v>
       </c>
       <c r="I16" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
@@ -1107,16 +1107,16 @@
         <v>0</v>
       </c>
       <c r="F17" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G17" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H17" t="s">
         <v>5</v>
       </c>
       <c r="I17" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
@@ -1131,13 +1131,13 @@
         <v>0</v>
       </c>
       <c r="F18" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H18" t="s">
         <v>5</v>
       </c>
       <c r="I18" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
@@ -1152,16 +1152,16 @@
         <v>0</v>
       </c>
       <c r="F19" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G19" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H19" t="s">
         <v>5</v>
       </c>
       <c r="I19" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
@@ -1176,16 +1176,16 @@
         <v>0</v>
       </c>
       <c r="F20" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G20" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H20" t="s">
         <v>5</v>
       </c>
       <c r="I20" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
@@ -1200,16 +1200,16 @@
         <v>0</v>
       </c>
       <c r="F21" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G21" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H21" t="s">
         <v>5</v>
       </c>
       <c r="I21" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>

--- a/tests/specs/fixtures/specs_groups.xlsx
+++ b/tests/specs/fixtures/specs_groups.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\MyPy\Packages\fltk\tests\specs\fixtures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B5296AB-2B88-4024-8546-BB9D828C181D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32823EA3-CB82-4051-B6BD-25C86A561DE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3810" yWindow="3810" windowWidth="28800" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="81">
   <si>
     <t>label</t>
   </si>
@@ -941,9 +941,7 @@
       <c r="G10" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="H10" s="2" t="s">
-        <v>5</v>
-      </c>
+      <c r="H10" s="2"/>
       <c r="I10" s="2" t="s">
         <v>5</v>
       </c>

--- a/tests/specs/fixtures/specs_groups.xlsx
+++ b/tests/specs/fixtures/specs_groups.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\MyPy\Packages\fltk\tests\specs\fixtures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32823EA3-CB82-4051-B6BD-25C86A561DE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3785928-9E88-48D4-BCCD-B57895D0BC64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3810" yWindow="3810" windowWidth="28800" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -22,8 +22,32 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Ephel</author>
+  </authors>
+  <commentList>
+    <comment ref="A22" authorId="0" shapeId="0" xr:uid="{F44AEB2F-4EA3-44F7-9BF9-4667AEF9530E}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>keep group with only one line for test</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="84">
   <si>
     <t>label</t>
   </si>
@@ -266,13 +290,22 @@
   </si>
   <si>
     <t>('q2021-4', 'q2022-4', 'q2023-4', 'q2024-4', 'q2025-4')</t>
+  </si>
+  <si>
+    <t>ratios</t>
+  </si>
+  <si>
+    <t>Ratios</t>
+  </si>
+  <si>
+    <t>fstypes</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -285,6 +318,13 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -635,8 +675,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J21"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:J22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.28515625" customWidth="1"/>
@@ -1210,9 +1250,24 @@
         <v>72</v>
       </c>
     </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>83</v>
+      </c>
+      <c r="B22" t="s">
+        <v>81</v>
+      </c>
+      <c r="C22" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="F22" t="s">
+        <v>82</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D2" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <conditionalFormatting sqref="C2:C21">
+  <conditionalFormatting sqref="C2:C22">
     <cfRule type="expression" dxfId="1" priority="1">
       <formula>C2=TRUE()</formula>
     </cfRule>
@@ -1222,5 +1277,6 @@
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>